--- a/compiler_practice_functions.xlsx
+++ b/compiler_practice_functions.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2605" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="919">
   <si>
     <t xml:space="preserve">Ассемблерные инструкции компиляторов по функциям</t>
   </si>
@@ -1246,40 +1246,46 @@
     <t xml:space="preserve">    cmpl    %r15d, %r14d</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB5_6        cmpl    %ebx, %r15d</t>
+    <t xml:space="preserve">    jge    .LBB5_6    </t>
   </si>
   <si>
     <t xml:space="preserve">    addq    $8, %rsp</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB5_5        cmpl    %ebp, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_7        addl    %ebp, %ebx</t>
+    <t xml:space="preserve">    cmpl    %ebx, %r15d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_5    </t>
   </si>
   <si>
     <t xml:space="preserve">    addl    %r13d, %eax</t>
   </si>
   <si>
+    <t xml:space="preserve">    cmpl    %ebp, %ebx</t>
+  </si>
+  <si>
     <t xml:space="preserve">    popq    %r13</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    -20(%rbp), %eax</t>
   </si>
   <si>
+    <t xml:space="preserve">    jge    .LBB5_7     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addq    $32, %rsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %r14d, %eax</t>
+  </si>
+  <si>
     <t xml:space="preserve">.LBB5_5:</t>
   </si>
   <si>
-    <t xml:space="preserve">    addq    $32, %rsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %r14d, %eax</t>
+    <t xml:space="preserve">.LFE5:</t>
   </si>
   <si>
     <t xml:space="preserve">.Lfunc_end5:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LFE5:</t>
   </si>
   <si>
     <t xml:space="preserve">.L18:</t>
@@ -2990,7 +2996,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3155,7 +3161,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3207,19 +3213,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3516,7 +3518,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -3539,7 +3541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="n">
         <v>1</v>
       </c>
@@ -3562,7 +3564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
@@ -3585,7 +3587,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
@@ -3608,7 +3610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
@@ -3626,7 +3628,7 @@
       </c>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
@@ -3651,7 +3653,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
@@ -3666,7 +3668,7 @@
       </c>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
@@ -3681,7 +3683,7 @@
       </c>
       <c r="G10" s="15"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
@@ -3696,7 +3698,7 @@
       </c>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
@@ -3711,7 +3713,7 @@
       </c>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
@@ -3726,7 +3728,7 @@
       </c>
       <c r="G13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
@@ -3756,7 +3758,7 @@
       </c>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
@@ -3771,7 +3773,7 @@
       </c>
       <c r="G16" s="15"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
@@ -3786,7 +3788,7 @@
       </c>
       <c r="G17" s="15"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
@@ -3795,7 +3797,7 @@
       </c>
       <c r="G18" s="15"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
@@ -3804,7 +3806,7 @@
       </c>
       <c r="G19" s="15"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
         <v>17</v>
       </c>
@@ -3817,7 +3819,7 @@
       <c r="F20" s="20"/>
       <c r="G20" s="21"/>
     </row>
-    <row r="21" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="26" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
         <v>37</v>
       </c>
@@ -3854,7 +3856,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
         <v>2</v>
       </c>
@@ -3877,7 +3879,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>1</v>
       </c>
@@ -3900,7 +3902,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="35" t="n">
         <v>2</v>
       </c>
@@ -3923,7 +3925,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="35" t="n">
         <v>3</v>
       </c>
@@ -3946,7 +3948,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="35" t="n">
         <v>4</v>
       </c>
@@ -3969,7 +3971,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="35" t="n">
         <v>5</v>
       </c>
@@ -3992,7 +3994,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="35" t="n">
         <v>6</v>
       </c>
@@ -4015,7 +4017,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="35" t="n">
         <v>7</v>
       </c>
@@ -4038,7 +4040,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="35" t="n">
         <v>8</v>
       </c>
@@ -4057,7 +4059,7 @@
       </c>
       <c r="G32" s="38"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="35" t="n">
         <v>9</v>
       </c>
@@ -4075,7 +4077,7 @@
       </c>
       <c r="G33" s="38"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="35" t="n">
         <v>10</v>
       </c>
@@ -4093,7 +4095,7 @@
       </c>
       <c r="G34" s="40"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="35" t="n">
         <v>11</v>
       </c>
@@ -4109,7 +4111,7 @@
       </c>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="35" t="n">
         <v>12</v>
       </c>
@@ -4125,7 +4127,7 @@
       </c>
       <c r="G36" s="40"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="35" t="n">
         <v>13</v>
       </c>
@@ -4141,7 +4143,7 @@
       </c>
       <c r="G37" s="40"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="35" t="n">
         <v>14</v>
       </c>
@@ -4157,7 +4159,7 @@
       </c>
       <c r="G38" s="40"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="35" t="n">
         <v>15</v>
       </c>
@@ -4173,7 +4175,7 @@
       </c>
       <c r="G39" s="40"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="35" t="n">
         <v>16</v>
       </c>
@@ -4196,7 +4198,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="35" t="n">
         <v>17</v>
       </c>
@@ -4212,7 +4214,7 @@
       </c>
       <c r="G41" s="40"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="35" t="n">
         <v>18</v>
       </c>
@@ -4228,7 +4230,7 @@
       </c>
       <c r="G42" s="40"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="35" t="n">
         <v>19</v>
       </c>
@@ -4244,7 +4246,7 @@
       </c>
       <c r="G43" s="40"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="35" t="n">
         <v>20</v>
       </c>
@@ -4260,7 +4262,7 @@
       </c>
       <c r="G44" s="40"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="35" t="n">
         <v>21</v>
       </c>
@@ -4276,7 +4278,7 @@
       </c>
       <c r="G45" s="40"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="35" t="n">
         <v>22</v>
       </c>
@@ -4308,7 +4310,7 @@
       </c>
       <c r="G47" s="40"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="35" t="n">
         <v>24</v>
       </c>
@@ -4324,7 +4326,7 @@
       </c>
       <c r="G48" s="40"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="35" t="n">
         <v>25</v>
       </c>
@@ -4340,7 +4342,7 @@
       </c>
       <c r="G49" s="40"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="35" t="n">
         <v>26</v>
       </c>
@@ -4356,7 +4358,7 @@
       </c>
       <c r="G50" s="40"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="35" t="n">
         <v>27</v>
       </c>
@@ -4372,7 +4374,7 @@
       </c>
       <c r="G51" s="40"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="35" t="n">
         <v>28</v>
       </c>
@@ -4388,7 +4390,7 @@
       </c>
       <c r="G52" s="40"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="35" t="n">
         <v>29</v>
       </c>
@@ -4401,7 +4403,7 @@
       <c r="F53" s="37"/>
       <c r="G53" s="15"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="35" t="n">
         <v>30</v>
       </c>
@@ -4411,7 +4413,7 @@
       <c r="F54" s="37"/>
       <c r="G54" s="15"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="35" t="n">
         <v>31</v>
       </c>
@@ -4421,7 +4423,7 @@
       <c r="F55" s="37"/>
       <c r="G55" s="15"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="35" t="n">
         <v>32</v>
       </c>
@@ -4431,7 +4433,7 @@
       <c r="F56" s="37"/>
       <c r="G56" s="15"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="35" t="n">
         <v>33</v>
       </c>
@@ -4440,7 +4442,7 @@
       </c>
       <c r="G57" s="15"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="35" t="n">
         <v>34</v>
       </c>
@@ -4449,7 +4451,7 @@
       </c>
       <c r="G58" s="15"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="43" t="n">
         <v>35</v>
       </c>
@@ -4462,7 +4464,7 @@
       <c r="F59" s="20"/>
       <c r="G59" s="21"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="22" t="s">
         <v>37</v>
       </c>
@@ -4479,7 +4481,7 @@
         <v>7</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>7</v>
@@ -4507,7 +4509,7 @@
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
         <v>2</v>
       </c>
@@ -4530,7 +4532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="47" t="n">
         <v>1</v>
       </c>
@@ -4553,7 +4555,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="48" t="n">
         <v>2</v>
       </c>
@@ -4576,7 +4578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="48" t="n">
         <v>3</v>
       </c>
@@ -4599,7 +4601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="48" t="n">
         <v>4</v>
       </c>
@@ -4622,7 +4624,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="48" t="n">
         <v>5</v>
       </c>
@@ -4645,7 +4647,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="48" t="n">
         <v>6</v>
       </c>
@@ -4668,7 +4670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="48" t="n">
         <v>7</v>
       </c>
@@ -4691,7 +4693,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="48" t="n">
         <v>8</v>
       </c>
@@ -4714,7 +4716,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="48" t="n">
         <v>9</v>
       </c>
@@ -4737,7 +4739,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="48" t="n">
         <v>10</v>
       </c>
@@ -4760,7 +4762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="48" t="n">
         <v>11</v>
       </c>
@@ -4783,7 +4785,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="48" t="n">
         <v>12</v>
       </c>
@@ -4806,7 +4808,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="48" t="n">
         <v>13</v>
       </c>
@@ -4829,7 +4831,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="48" t="n">
         <v>14</v>
       </c>
@@ -4852,7 +4854,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="48" t="n">
         <v>15</v>
       </c>
@@ -4875,7 +4877,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="48" t="n">
         <v>16</v>
       </c>
@@ -4898,7 +4900,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="48" t="n">
         <v>17</v>
       </c>
@@ -4921,7 +4923,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="48" t="n">
         <v>18</v>
       </c>
@@ -4944,7 +4946,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="48" t="n">
         <v>19</v>
       </c>
@@ -4967,7 +4969,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="48" t="n">
         <v>20</v>
       </c>
@@ -4990,7 +4992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="48" t="n">
         <v>21</v>
       </c>
@@ -5013,7 +5015,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="48" t="n">
         <v>22</v>
       </c>
@@ -5036,7 +5038,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="48" t="n">
         <v>23</v>
       </c>
@@ -5059,7 +5061,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="48" t="n">
         <v>24</v>
       </c>
@@ -5082,7 +5084,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="48" t="n">
         <v>25</v>
       </c>
@@ -5105,7 +5107,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="48" t="n">
         <v>26</v>
       </c>
@@ -5128,7 +5130,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="48" t="n">
         <v>27</v>
       </c>
@@ -5151,7 +5153,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="48" t="n">
         <v>28</v>
       </c>
@@ -5174,7 +5176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="48" t="n">
         <v>29</v>
       </c>
@@ -5197,7 +5199,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="48" t="n">
         <v>30</v>
       </c>
@@ -5220,7 +5222,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="48" t="n">
         <v>31</v>
       </c>
@@ -5243,7 +5245,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="48" t="n">
         <v>32</v>
       </c>
@@ -5266,7 +5268,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="48" t="n">
         <v>33</v>
       </c>
@@ -5289,7 +5291,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="48" t="n">
         <v>34</v>
       </c>
@@ -5312,7 +5314,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="48" t="n">
         <v>35</v>
       </c>
@@ -5335,7 +5337,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="48" t="n">
         <v>36</v>
       </c>
@@ -5358,7 +5360,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="48" t="n">
         <v>37</v>
       </c>
@@ -5381,7 +5383,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="48" t="n">
         <v>38</v>
       </c>
@@ -5404,7 +5406,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="48" t="n">
         <v>39</v>
       </c>
@@ -5427,7 +5429,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="48" t="n">
         <v>40</v>
       </c>
@@ -5450,7 +5452,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="48" t="n">
         <v>41</v>
       </c>
@@ -5473,7 +5475,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="48" t="n">
         <v>42</v>
       </c>
@@ -5496,7 +5498,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="48" t="n">
         <v>43</v>
       </c>
@@ -5526,7 +5528,7 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="48" t="n">
         <v>44</v>
       </c>
@@ -5549,7 +5551,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="48" t="n">
         <v>45</v>
       </c>
@@ -5572,7 +5574,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="48" t="n">
         <v>46</v>
       </c>
@@ -5592,7 +5594,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="48" t="n">
         <v>47</v>
       </c>
@@ -5610,7 +5612,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="48" t="n">
         <v>48</v>
       </c>
@@ -5626,7 +5628,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="48" t="n">
         <v>49</v>
       </c>
@@ -5654,7 +5656,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="48" t="n">
         <v>51</v>
       </c>
@@ -5668,7 +5670,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="48" t="n">
         <v>52</v>
       </c>
@@ -5679,7 +5681,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="48" t="n">
         <v>53</v>
       </c>
@@ -5690,7 +5692,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="48" t="n">
         <v>54</v>
       </c>
@@ -5701,7 +5703,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="48" t="n">
         <v>55</v>
       </c>
@@ -5712,7 +5714,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="48" t="n">
         <v>56</v>
       </c>
@@ -5723,7 +5725,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="48" t="n">
         <v>57</v>
       </c>
@@ -5734,7 +5736,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="48" t="n">
         <v>58</v>
       </c>
@@ -5745,7 +5747,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="48" t="n">
         <v>59</v>
       </c>
@@ -5756,7 +5758,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="48" t="n">
         <v>60</v>
       </c>
@@ -5767,7 +5769,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="48" t="n">
         <v>61</v>
       </c>
@@ -5776,7 +5778,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="48" t="n">
         <v>62</v>
       </c>
@@ -5785,7 +5787,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="48" t="n">
         <v>63</v>
       </c>
@@ -5794,7 +5796,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="48" t="n">
         <v>64</v>
       </c>
@@ -5803,7 +5805,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="48" t="n">
         <v>65</v>
       </c>
@@ -5812,7 +5814,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="48" t="n">
         <v>66</v>
       </c>
@@ -5821,7 +5823,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="48" t="n">
         <v>67</v>
       </c>
@@ -5830,7 +5832,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="48" t="n">
         <v>68</v>
       </c>
@@ -5839,7 +5841,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="48" t="n">
         <v>69</v>
       </c>
@@ -5848,7 +5850,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="48" t="n">
         <v>70</v>
       </c>
@@ -5857,7 +5859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="48" t="n">
         <v>71</v>
       </c>
@@ -5866,7 +5868,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="48" t="n">
         <v>72</v>
       </c>
@@ -5875,7 +5877,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="48" t="n">
         <v>73</v>
       </c>
@@ -5884,7 +5886,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="48" t="n">
         <v>74</v>
       </c>
@@ -5893,7 +5895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="48" t="n">
         <v>75</v>
       </c>
@@ -5902,7 +5904,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="48" t="n">
         <v>76</v>
       </c>
@@ -5911,7 +5913,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="48" t="n">
         <v>77</v>
       </c>
@@ -5920,7 +5922,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="48" t="n">
         <v>78</v>
       </c>
@@ -5929,7 +5931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="48" t="n">
         <v>79</v>
       </c>
@@ -5938,7 +5940,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="48" t="n">
         <v>80</v>
       </c>
@@ -5947,7 +5949,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="48" t="n">
         <v>81</v>
       </c>
@@ -5963,7 +5965,7 @@
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="50" t="n">
         <v>82</v>
       </c>
@@ -5976,7 +5978,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="22" t="s">
         <v>37</v>
       </c>
@@ -6021,7 +6023,7 @@
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="27" t="s">
         <v>2</v>
       </c>
@@ -6044,7 +6046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="47" t="n">
         <v>1</v>
       </c>
@@ -6090,7 +6092,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="48" t="n">
         <v>3</v>
       </c>
@@ -6113,7 +6115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="48" t="n">
         <v>4</v>
       </c>
@@ -6136,7 +6138,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="48" t="n">
         <v>5</v>
       </c>
@@ -6159,7 +6161,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="48" t="n">
         <v>6</v>
       </c>
@@ -6182,7 +6184,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="48" t="n">
         <v>7</v>
       </c>
@@ -6205,7 +6207,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="48" t="n">
         <v>8</v>
       </c>
@@ -6228,7 +6230,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="48" t="n">
         <v>9</v>
       </c>
@@ -6251,7 +6253,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="48" t="n">
         <v>10</v>
       </c>
@@ -6274,7 +6276,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="48" t="n">
         <v>11</v>
       </c>
@@ -6297,7 +6299,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="48" t="n">
         <v>12</v>
       </c>
@@ -6320,7 +6322,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="48" t="n">
         <v>13</v>
       </c>
@@ -6343,7 +6345,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="48" t="n">
         <v>14</v>
       </c>
@@ -6366,7 +6368,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="48" t="n">
         <v>15</v>
       </c>
@@ -6389,7 +6391,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="48" t="n">
         <v>16</v>
       </c>
@@ -6412,7 +6414,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="48" t="n">
         <v>17</v>
       </c>
@@ -6435,7 +6437,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="48" t="n">
         <v>18</v>
       </c>
@@ -6458,7 +6460,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="48" t="n">
         <v>19</v>
       </c>
@@ -6481,7 +6483,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="48" t="n">
         <v>20</v>
       </c>
@@ -6504,7 +6506,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="48" t="n">
         <v>21</v>
       </c>
@@ -6527,7 +6529,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="48" t="n">
         <v>22</v>
       </c>
@@ -6550,7 +6552,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="48" t="n">
         <v>23</v>
       </c>
@@ -6573,7 +6575,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="48" t="n">
         <v>24</v>
       </c>
@@ -6596,7 +6598,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="48" t="n">
         <v>25</v>
       </c>
@@ -6619,7 +6621,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="48" t="n">
         <v>26</v>
       </c>
@@ -6642,7 +6644,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="48" t="n">
         <v>27</v>
       </c>
@@ -6665,7 +6667,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="48" t="n">
         <v>28</v>
       </c>
@@ -6686,7 +6688,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="48" t="n">
         <v>29</v>
       </c>
@@ -6705,7 +6707,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="48" t="n">
         <v>30</v>
       </c>
@@ -6724,7 +6726,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="48" t="n">
         <v>31</v>
       </c>
@@ -6743,7 +6745,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="48" t="n">
         <v>32</v>
       </c>
@@ -6760,7 +6762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="48" t="n">
         <v>33</v>
       </c>
@@ -6777,7 +6779,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="48" t="n">
         <v>34</v>
       </c>
@@ -6794,7 +6796,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="48" t="n">
         <v>35</v>
       </c>
@@ -6809,7 +6811,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="48" t="n">
         <v>36</v>
       </c>
@@ -6824,7 +6826,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="48" t="n">
         <v>37</v>
       </c>
@@ -6839,7 +6841,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="48" t="n">
         <v>38</v>
       </c>
@@ -6854,7 +6856,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="48" t="n">
         <v>39</v>
       </c>
@@ -6869,7 +6871,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="48" t="n">
         <v>40</v>
       </c>
@@ -6910,7 +6912,7 @@
       <c r="F191" s="20"/>
       <c r="G191" s="21"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="22" t="s">
         <v>37</v>
       </c>
@@ -6955,7 +6957,7 @@
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="27" t="s">
         <v>2</v>
       </c>
@@ -6978,7 +6980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="47" t="n">
         <v>1</v>
       </c>
@@ -7001,7 +7003,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="48" t="n">
         <v>2</v>
       </c>
@@ -7024,7 +7026,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="48" t="n">
         <v>3</v>
       </c>
@@ -7047,7 +7049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="48" t="n">
         <v>4</v>
       </c>
@@ -7070,7 +7072,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="48" t="n">
         <v>5</v>
       </c>
@@ -7093,7 +7095,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="48" t="n">
         <v>6</v>
       </c>
@@ -7116,7 +7118,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="48" t="n">
         <v>7</v>
       </c>
@@ -7139,7 +7141,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="48" t="n">
         <v>8</v>
       </c>
@@ -7162,7 +7164,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="48" t="n">
         <v>9</v>
       </c>
@@ -7185,7 +7187,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="48" t="n">
         <v>10</v>
       </c>
@@ -7208,7 +7210,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="48" t="n">
         <v>11</v>
       </c>
@@ -7231,7 +7233,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="48" t="n">
         <v>12</v>
       </c>
@@ -7254,7 +7256,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="48" t="n">
         <v>13</v>
       </c>
@@ -7277,7 +7279,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="48" t="n">
         <v>14</v>
       </c>
@@ -7307,7 +7309,7 @@
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="48" t="n">
         <v>15</v>
       </c>
@@ -7337,7 +7339,7 @@
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="48" t="n">
         <v>16</v>
       </c>
@@ -7367,7 +7369,7 @@
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="48" t="n">
         <v>17</v>
       </c>
@@ -7397,7 +7399,7 @@
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="48" t="n">
         <v>18</v>
       </c>
@@ -7427,7 +7429,7 @@
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="48" t="n">
         <v>19</v>
       </c>
@@ -7450,7 +7452,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="48" t="n">
         <v>20</v>
       </c>
@@ -7473,7 +7475,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="48" t="n">
         <v>21</v>
       </c>
@@ -7496,7 +7498,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="48" t="n">
         <v>22</v>
       </c>
@@ -7519,7 +7521,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="48" t="n">
         <v>23</v>
       </c>
@@ -7542,7 +7544,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="48" t="n">
         <v>24</v>
       </c>
@@ -7565,7 +7567,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="48" t="n">
         <v>25</v>
       </c>
@@ -7588,7 +7590,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="48" t="n">
         <v>26</v>
       </c>
@@ -7611,7 +7613,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="48" t="n">
         <v>27</v>
       </c>
@@ -7634,7 +7636,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="48" t="n">
         <v>28</v>
       </c>
@@ -7657,7 +7659,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="48" t="n">
         <v>29</v>
       </c>
@@ -7680,7 +7682,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="48" t="n">
         <v>30</v>
       </c>
@@ -7703,7 +7705,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="48" t="n">
         <v>31</v>
       </c>
@@ -7726,7 +7728,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="48" t="n">
         <v>32</v>
       </c>
@@ -7749,7 +7751,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="48" t="n">
         <v>33</v>
       </c>
@@ -7772,7 +7774,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="48" t="n">
         <v>34</v>
       </c>
@@ -7795,7 +7797,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="48" t="n">
         <v>35</v>
       </c>
@@ -7818,7 +7820,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="48" t="n">
         <v>36</v>
       </c>
@@ -7841,7 +7843,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="48" t="n">
         <v>37</v>
       </c>
@@ -7864,7 +7866,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="48" t="n">
         <v>38</v>
       </c>
@@ -7887,7 +7889,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="48" t="n">
         <v>39</v>
       </c>
@@ -7910,7 +7912,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="48" t="n">
         <v>40</v>
       </c>
@@ -7933,7 +7935,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="48" t="n">
         <v>41</v>
       </c>
@@ -7956,7 +7958,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="48" t="n">
         <v>42</v>
       </c>
@@ -7979,7 +7981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="48" t="n">
         <v>43</v>
       </c>
@@ -8002,7 +8004,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="48" t="n">
         <v>44</v>
       </c>
@@ -8025,7 +8027,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="48" t="n">
         <v>45</v>
       </c>
@@ -8048,7 +8050,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="48" t="n">
         <v>46</v>
       </c>
@@ -8071,7 +8073,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="48" t="n">
         <v>47</v>
       </c>
@@ -8094,7 +8096,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="48" t="n">
         <v>48</v>
       </c>
@@ -8117,7 +8119,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="48" t="n">
         <v>49</v>
       </c>
@@ -8140,7 +8142,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="48" t="n">
         <v>50</v>
       </c>
@@ -8163,7 +8165,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="48" t="n">
         <v>51</v>
       </c>
@@ -8186,7 +8188,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="48" t="n">
         <v>52</v>
       </c>
@@ -8209,7 +8211,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="48" t="n">
         <v>53</v>
       </c>
@@ -8232,7 +8234,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="48" t="n">
         <v>54</v>
       </c>
@@ -8255,7 +8257,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="48" t="n">
         <v>55</v>
       </c>
@@ -8278,7 +8280,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="48" t="n">
         <v>56</v>
       </c>
@@ -8320,7 +8322,7 @@
       <c r="F252" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="G252" s="38" t="s">
+      <c r="G252" s="54" t="s">
         <v>410</v>
       </c>
     </row>
@@ -8343,11 +8345,11 @@
       <c r="F253" s="37" t="s">
         <v>356</v>
       </c>
-      <c r="G253" s="38" t="s">
+      <c r="G253" s="54" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="48" t="n">
         <v>59</v>
       </c>
@@ -8367,7 +8369,7 @@
         <v>324</v>
       </c>
       <c r="G254" s="38" t="s">
-        <v>348</v>
+        <v>413</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8378,22 +8380,22 @@
         <v>68</v>
       </c>
       <c r="C255" s="37" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D255" s="37" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E255" s="37" t="s">
         <v>273</v>
       </c>
       <c r="F255" s="37" t="s">
-        <v>414</v>
-      </c>
-      <c r="G255" s="38" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G255" s="54" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="48" t="n">
         <v>61</v>
       </c>
@@ -8404,19 +8406,19 @@
         <v>15</v>
       </c>
       <c r="D256" s="37" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E256" s="37" t="s">
         <v>354</v>
       </c>
       <c r="F256" s="37" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G256" s="38" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="48" t="n">
         <v>62</v>
       </c>
@@ -8424,7 +8426,7 @@
         <v>35</v>
       </c>
       <c r="C257" s="37" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D257" s="37" t="s">
         <v>32</v>
@@ -8439,7 +8441,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="48" t="n">
         <v>63</v>
       </c>
@@ -8453,16 +8455,16 @@
         <v>34</v>
       </c>
       <c r="E258" s="37" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F258" s="37" t="s">
         <v>34</v>
       </c>
       <c r="G258" s="38" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="48" t="n">
         <v>64</v>
       </c>
@@ -8481,30 +8483,34 @@
       <c r="F259" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G259" s="38"/>
-    </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G259" s="38" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="48" t="n">
         <v>65</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C260" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D260" s="37" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E260" s="37" t="s">
         <v>196</v>
       </c>
       <c r="F260" s="37" t="s">
-        <v>418</v>
-      </c>
-      <c r="G260" s="38"/>
-    </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>421</v>
+      </c>
+      <c r="G260" s="38" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="48" t="n">
         <v>66</v>
       </c>
@@ -8517,9 +8523,11 @@
         <v>103</v>
       </c>
       <c r="F261" s="37"/>
-      <c r="G261" s="40"/>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G261" s="38" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="48" t="n">
         <v>67</v>
       </c>
@@ -8532,59 +8540,59 @@
       </c>
       <c r="G262" s="40"/>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="48" t="n">
         <v>68</v>
       </c>
       <c r="B263" s="14"/>
       <c r="C263" s="37" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E263" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G263" s="40"/>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="48" t="n">
         <v>69</v>
       </c>
       <c r="B264" s="14"/>
       <c r="C264" s="37" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E264" s="37" t="s">
         <v>32</v>
       </c>
       <c r="G264" s="40"/>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="48" t="n">
         <v>70</v>
       </c>
       <c r="B265" s="14"/>
       <c r="C265" s="37" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E265" s="37" t="s">
         <v>188</v>
       </c>
       <c r="G265" s="40"/>
     </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="48" t="n">
         <v>71</v>
       </c>
       <c r="B266" s="14"/>
       <c r="C266" s="37" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E266" s="37" t="s">
         <v>13</v>
       </c>
       <c r="G266" s="40"/>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="48" t="n">
         <v>72</v>
       </c>
@@ -8593,11 +8601,11 @@
         <v>323</v>
       </c>
       <c r="E267" s="37" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G267" s="40"/>
     </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="48" t="n">
         <v>73</v>
       </c>
@@ -8610,7 +8618,7 @@
       </c>
       <c r="G268" s="40"/>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="48" t="n">
         <v>74</v>
       </c>
@@ -8623,33 +8631,33 @@
       </c>
       <c r="G269" s="40"/>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="48" t="n">
         <v>75</v>
       </c>
       <c r="B270" s="14"/>
       <c r="C270" s="37" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E270" s="37" t="s">
         <v>387</v>
       </c>
       <c r="G270" s="40"/>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="48" t="n">
         <v>76</v>
       </c>
       <c r="B271" s="14"/>
       <c r="C271" s="37" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E271" s="37" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G271" s="40"/>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="48" t="n">
         <v>77</v>
       </c>
@@ -8659,20 +8667,20 @@
       </c>
       <c r="G272" s="40"/>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="50" t="n">
         <v>78</v>
       </c>
       <c r="B273" s="51"/>
-      <c r="C273" s="54" t="s">
-        <v>426</v>
+      <c r="C273" s="55" t="s">
+        <v>428</v>
       </c>
       <c r="D273" s="20"/>
       <c r="E273" s="20"/>
       <c r="F273" s="20"/>
       <c r="G273" s="21"/>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="22" t="s">
         <v>37</v>
       </c>
@@ -8692,7 +8700,7 @@
         <v>65</v>
       </c>
       <c r="G274" s="25" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H274" s="26"/>
       <c r="I274" s="26"/>
@@ -8705,7 +8713,7 @@
     </row>
     <row r="276" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -8714,7 +8722,7 @@
       <c r="F276" s="4"/>
       <c r="G276" s="4"/>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
         <v>2</v>
       </c>
@@ -8737,18 +8745,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E278" s="11" t="s">
         <v>11</v>
@@ -8760,7 +8768,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="13" t="n">
         <v>2</v>
       </c>
@@ -8783,7 +8791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="13" t="n">
         <v>3</v>
       </c>
@@ -8806,7 +8814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="13" t="n">
         <v>4</v>
       </c>
@@ -8829,7 +8837,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="13" t="n">
         <v>5</v>
       </c>
@@ -8852,7 +8860,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="13" t="n">
         <v>6</v>
       </c>
@@ -8875,7 +8883,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="13" t="n">
         <v>7</v>
       </c>
@@ -8883,7 +8891,7 @@
         <v>23</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>49</v>
@@ -8898,7 +8906,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="13" t="n">
         <v>8</v>
       </c>
@@ -8921,7 +8929,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="13" t="n">
         <v>9</v>
       </c>
@@ -8929,22 +8937,22 @@
         <v>24</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G286" s="15" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="13" t="n">
         <v>10</v>
       </c>
@@ -8958,7 +8966,7 @@
         <v>26</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>26</v>
@@ -8967,53 +8975,53 @@
         <v>105</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="13" t="n">
         <v>11</v>
       </c>
       <c r="B288" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C288" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D288" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G288" s="15" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="13" t="n">
         <v>12</v>
       </c>
       <c r="B289" s="14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G289" s="15" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="13" t="n">
         <v>13</v>
       </c>
@@ -9021,7 +9029,7 @@
         <v>88</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>47</v>
@@ -9036,7 +9044,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="13" t="n">
         <v>14</v>
       </c>
@@ -9044,7 +9052,7 @@
         <v>89</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>82</v>
@@ -9059,7 +9067,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="13" t="n">
         <v>15</v>
       </c>
@@ -9067,13 +9075,13 @@
         <v>90</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>84</v>
@@ -9082,7 +9090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="13" t="n">
         <v>16</v>
       </c>
@@ -9090,191 +9098,191 @@
         <v>91</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G293" s="15" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B294" s="55" t="s">
+      <c r="B294" s="56" t="s">
         <v>93</v>
       </c>
       <c r="C294" s="53" t="s">
         <v>79</v>
       </c>
       <c r="D294" s="53" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E294" s="53" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F294" s="53" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G294" s="40" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B295" s="0" t="s">
-        <v>451</v>
-      </c>
-      <c r="C295" s="0" t="s">
+      <c r="B295" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D295" s="0" t="s">
-        <v>452</v>
-      </c>
-      <c r="E295" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="F295" s="0" t="s">
-        <v>452</v>
-      </c>
-      <c r="G295" s="56" t="s">
+      <c r="D295" s="2" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E295" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F295" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G295" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="13" t="n">
         <v>19</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G296" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="13" t="n">
         <v>20</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G297" s="15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="13" t="n">
         <v>21</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G298" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="13" t="n">
         <v>22</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G299" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="13" t="n">
         <v>23</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G300" s="15" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="13" t="n">
         <v>24</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>47</v>
@@ -9286,41 +9294,41 @@
         <v>80</v>
       </c>
       <c r="G301" s="15" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="13" t="n">
         <v>25</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G302" s="15" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="13" t="n">
         <v>26</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>86</v>
@@ -9332,33 +9340,33 @@
         <v>84</v>
       </c>
       <c r="G303" s="15" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="13" t="n">
         <v>27</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>251</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G304" s="15" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="13" t="n">
         <v>28</v>
       </c>
@@ -9366,7 +9374,7 @@
         <v>88</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>85</v>
@@ -9375,13 +9383,13 @@
         <v>47</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G305" s="15" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="13" t="n">
         <v>29</v>
       </c>
@@ -9389,22 +9397,22 @@
         <v>89</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G306" s="15" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="13" t="n">
         <v>30</v>
       </c>
@@ -9412,22 +9420,22 @@
         <v>90</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G307" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="13" t="n">
         <v>31</v>
       </c>
@@ -9435,22 +9443,22 @@
         <v>91</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>80</v>
       </c>
       <c r="G308" s="15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="13" t="n">
         <v>32</v>
       </c>
@@ -9458,13 +9466,13 @@
         <v>93</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>82</v>
@@ -9473,12 +9481,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="13" t="n">
         <v>33</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>71</v>
@@ -9487,7 +9495,7 @@
         <v>86</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>84</v>
@@ -9496,7 +9504,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="13" t="n">
         <v>34</v>
       </c>
@@ -9507,65 +9515,65 @@
         <v>187</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G311" s="15" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="13" t="n">
         <v>35</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G312" s="15" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="13" t="n">
         <v>36</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G313" s="15" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="13" t="n">
         <v>37</v>
       </c>
@@ -9573,22 +9581,22 @@
         <v>88</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G314" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="13" t="n">
         <v>38</v>
       </c>
@@ -9596,45 +9604,45 @@
         <v>89</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G315" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="B316" s="0" t="s">
+      <c r="B316" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C316" s="0" t="s">
-        <v>496</v>
-      </c>
-      <c r="D316" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="E316" s="0" t="s">
+      <c r="C316" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F316" s="0" t="s">
-        <v>490</v>
+      <c r="F316" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="G316" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="13" t="n">
         <v>40</v>
       </c>
@@ -9642,22 +9650,22 @@
         <v>91</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G317" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="13" t="n">
         <v>41</v>
       </c>
@@ -9665,59 +9673,59 @@
         <v>93</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G318" s="15" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="13" t="n">
         <v>42</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>80</v>
       </c>
       <c r="G319" s="15" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="13" t="n">
         <v>43</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>82</v>
@@ -9726,153 +9734,153 @@
         <v>358</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="13" t="n">
         <v>44</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G321" s="15" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="13" t="n">
         <v>45</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G322" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="13" t="n">
         <v>46</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G323" s="15" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="13" t="n">
         <v>47</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G324" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="13" t="n">
         <v>48</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G325" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="13" t="n">
         <v>49</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G326" s="15" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="13" t="n">
         <v>50</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>71</v>
@@ -9884,33 +9892,33 @@
         <v>144</v>
       </c>
       <c r="G327" s="15" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="13" t="n">
         <v>51</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G328" s="15" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="13" t="n">
         <v>52</v>
       </c>
@@ -9918,22 +9926,22 @@
         <v>88</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G329" s="15" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="13" t="n">
         <v>53</v>
       </c>
@@ -9947,16 +9955,16 @@
         <v>71</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>144</v>
       </c>
       <c r="G330" s="15" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="13" t="n">
         <v>54</v>
       </c>
@@ -9964,22 +9972,22 @@
         <v>90</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G331" s="15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="13" t="n">
         <v>55</v>
       </c>
@@ -9987,22 +9995,22 @@
         <v>91</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G332" s="15" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="13" t="n">
         <v>56</v>
       </c>
@@ -10010,59 +10018,59 @@
         <v>93</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G333" s="15" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="13" t="n">
         <v>57</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G334" s="15" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="13" t="n">
         <v>58</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>144</v>
@@ -10071,76 +10079,76 @@
         <v>187</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="13" t="n">
         <v>59</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G336" s="15" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="13" t="n">
         <v>60</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G337" s="15" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="13" t="n">
         <v>61</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G338" s="15" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="13" t="n">
         <v>62</v>
       </c>
@@ -10154,39 +10162,39 @@
         <v>168</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F339" s="2" t="s">
         <v>170</v>
       </c>
       <c r="G339" s="15" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="13" t="n">
         <v>63</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G340" s="15" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="13" t="n">
         <v>64</v>
       </c>
@@ -10194,45 +10202,45 @@
         <v>71</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G341" s="15" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="13" t="n">
         <v>65</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G342" s="15" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="13" t="n">
         <v>66</v>
       </c>
@@ -10240,45 +10248,45 @@
         <v>71</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G343" s="15" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="13" t="n">
         <v>67</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G344" s="15" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="13" t="n">
         <v>68</v>
       </c>
@@ -10286,303 +10294,303 @@
         <v>187</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G345" s="15" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="13" t="n">
         <v>69</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G346" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="13" t="n">
         <v>70</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G347" s="15" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="13" t="n">
         <v>71</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G348" s="15" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="13" t="n">
         <v>72</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G349" s="15" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="13" t="n">
         <v>73</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G350" s="15" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="13" t="n">
         <v>74</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G351" s="15" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="13" t="n">
         <v>75</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G352" s="15" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="13" t="n">
         <v>76</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G353" s="15" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="13" t="n">
         <v>77</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C354" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F354" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D354" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E354" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>590</v>
-      </c>
       <c r="G354" s="15" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="13" t="n">
         <v>78</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G355" s="15" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="13" t="n">
         <v>79</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G356" s="15" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="13" t="n">
         <v>80</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G357" s="15" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="13" t="n">
         <v>81</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>44</v>
@@ -10591,159 +10599,175 @@
         <v>54</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G358" s="15" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="13" t="n">
         <v>82</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G359" s="15" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="13" t="n">
         <v>83</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G360" s="15" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="13" t="n">
         <v>84</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>144</v>
       </c>
       <c r="G361" s="15" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="13" t="n">
         <v>85</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G362" s="15" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="363" s="41" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="13" t="n">
         <v>86</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="G363" s="15" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="364" s="57" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>620</v>
+      </c>
+      <c r="H363" s="0"/>
+      <c r="I363" s="0"/>
+      <c r="J363" s="0"/>
+      <c r="K363" s="0"/>
+      <c r="L363" s="0"/>
+      <c r="M363" s="0"/>
+      <c r="N363" s="0"/>
+      <c r="O363" s="0"/>
+    </row>
+    <row r="364" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="13" t="n">
         <v>87</v>
       </c>
-      <c r="B364" s="55" t="s">
-        <v>518</v>
-      </c>
-      <c r="C364" s="55" t="s">
+      <c r="B364" s="56" t="s">
+        <v>520</v>
+      </c>
+      <c r="C364" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D364" s="55" t="s">
+      <c r="D364" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="E364" s="55" t="s">
-        <v>619</v>
-      </c>
-      <c r="F364" s="55" t="s">
+      <c r="E364" s="56" t="s">
+        <v>621</v>
+      </c>
+      <c r="F364" s="56" t="s">
         <v>227</v>
       </c>
       <c r="G364" s="15" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>622</v>
+      </c>
+      <c r="H364" s="41"/>
+      <c r="I364" s="41"/>
+      <c r="J364" s="41"/>
+      <c r="K364" s="41"/>
+      <c r="L364" s="41"/>
+      <c r="M364" s="41"/>
+      <c r="N364" s="41"/>
+      <c r="O364" s="41"/>
+    </row>
+    <row r="365" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="13" t="n">
         <v>88</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>93</v>
@@ -10755,13 +10779,13 @@
         <v>221</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="G365" s="15" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="13" t="n">
         <v>89</v>
       </c>
@@ -10769,10 +10793,10 @@
         <v>54</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>237</v>
@@ -10781,15 +10805,15 @@
         <v>144</v>
       </c>
       <c r="G366" s="15" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="13" t="n">
         <v>90</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>46</v>
@@ -10798,16 +10822,16 @@
         <v>71</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F367" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G367" s="15" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="13" t="n">
         <v>91</v>
       </c>
@@ -10827,10 +10851,10 @@
         <v>73</v>
       </c>
       <c r="G368" s="15" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="13" t="n">
         <v>92</v>
       </c>
@@ -10838,7 +10862,7 @@
         <v>71</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>74</v>
@@ -10847,36 +10871,36 @@
         <v>86</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G369" s="15" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="13" t="n">
         <v>93</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G370" s="15" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="13" t="n">
         <v>94</v>
       </c>
@@ -10884,45 +10908,45 @@
         <v>71</v>
       </c>
       <c r="C371" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D371" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="D371" s="2" t="s">
-        <v>632</v>
-      </c>
       <c r="E371" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G371" s="15" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="13" t="n">
         <v>95</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G372" s="15" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="13" t="n">
         <v>96</v>
       </c>
@@ -10933,19 +10957,19 @@
         <v>241</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G373" s="15" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="13" t="n">
         <v>97</v>
       </c>
@@ -10953,7 +10977,7 @@
         <v>228</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>85</v>
@@ -10962,13 +10986,13 @@
         <v>44</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G374" s="15" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="13" t="n">
         <v>98</v>
       </c>
@@ -10976,10 +11000,10 @@
         <v>226</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>86</v>
@@ -10991,30 +11015,30 @@
         <v>48</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="13" t="n">
         <v>99</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G376" s="15" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="13" t="n">
         <v>100</v>
       </c>
@@ -11025,10 +11049,10 @@
         <v>280</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F377" s="2" t="s">
         <v>72</v>
@@ -11037,7 +11061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="13" t="n">
         <v>101</v>
       </c>
@@ -11045,7 +11069,7 @@
         <v>72</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>72</v>
@@ -11054,13 +11078,13 @@
         <v>237</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G378" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="13" t="n">
         <v>102</v>
       </c>
@@ -11071,42 +11095,42 @@
         <v>223</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G379" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="13" t="n">
         <v>103</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G380" s="15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="13" t="n">
         <v>104</v>
       </c>
@@ -11117,19 +11141,19 @@
         <v>110</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G381" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="13" t="n">
         <v>105</v>
       </c>
@@ -11140,19 +11164,19 @@
         <v>113</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G382" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="13" t="n">
         <v>106</v>
       </c>
@@ -11163,65 +11187,65 @@
         <v>384</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G383" s="15" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="13" t="n">
         <v>107</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G384" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="13" t="n">
         <v>108</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G385" s="15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="13" t="n">
         <v>109</v>
       </c>
@@ -11229,10 +11253,10 @@
         <v>150</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>86</v>
@@ -11244,7 +11268,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="13" t="n">
         <v>110</v>
       </c>
@@ -11258,39 +11282,39 @@
         <v>54</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G387" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="13" t="n">
         <v>111</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G388" s="15" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="13" t="n">
         <v>112</v>
       </c>
@@ -11298,45 +11322,45 @@
         <v>69</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G389" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="13" t="n">
         <v>113</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F390" s="2" t="s">
         <v>144</v>
       </c>
       <c r="G390" s="15" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="13" t="n">
         <v>114</v>
       </c>
@@ -11350,99 +11374,99 @@
         <v>71</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G391" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="13" t="n">
         <v>115</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G392" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="13" t="n">
         <v>116</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C393" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D393" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D393" s="2" t="s">
-        <v>679</v>
-      </c>
       <c r="E393" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F393" s="2" t="s">
         <v>219</v>
       </c>
       <c r="G393" s="15" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="13" t="n">
         <v>117</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G394" s="15" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="13" t="n">
         <v>118</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>144</v>
@@ -11451,30 +11475,30 @@
         <v>241</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="13" t="n">
         <v>119</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F396" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G396" s="15" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="13" t="n">
         <v>120</v>
       </c>
@@ -11482,30 +11506,30 @@
         <v>64</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F397" s="2" t="s">
         <v>73</v>
       </c>
       <c r="G397" s="15" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="13" t="n">
         <v>121</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>72</v>
@@ -11514,21 +11538,21 @@
         <v>221</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G398" s="15" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="13" t="n">
         <v>122</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>74</v>
@@ -11537,105 +11561,105 @@
         <v>237</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G399" s="15" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="13" t="n">
         <v>123</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G400" s="15" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="13" t="n">
         <v>124</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G401" s="15" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="13" t="n">
         <v>125</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G402" s="15" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="13" t="n">
         <v>126</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G403" s="15" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="13" t="n">
         <v>127</v>
       </c>
@@ -11643,22 +11667,22 @@
         <v>168</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G404" s="15" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="13" t="n">
         <v>128</v>
       </c>
@@ -11666,68 +11690,68 @@
         <v>85</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G405" s="15" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="406" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="13" t="n">
         <v>129</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G406" s="15" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="13" t="n">
         <v>130</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G407" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="13" t="n">
         <v>131</v>
       </c>
@@ -11738,30 +11762,30 @@
         <v>44</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G408" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="13" t="n">
         <v>132</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>185</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>86</v>
@@ -11770,33 +11794,33 @@
         <v>134</v>
       </c>
       <c r="G409" s="15" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="13" t="n">
         <v>133</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>399</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G410" s="15" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="13" t="n">
         <v>134</v>
       </c>
@@ -11810,50 +11834,50 @@
         <v>69</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G411" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="13" t="n">
         <v>135</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G412" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="13" t="n">
         <v>136</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>221</v>
@@ -11865,7 +11889,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="13" t="n">
         <v>137</v>
       </c>
@@ -11873,10 +11897,10 @@
         <v>219</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>44</v>
@@ -11888,15 +11912,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="13" t="n">
         <v>138</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>47</v>
@@ -11908,15 +11932,15 @@
         <v>84</v>
       </c>
       <c r="G415" s="15" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="13" t="n">
         <v>139</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>46</v>
@@ -11925,39 +11949,39 @@
         <v>82</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G416" s="15" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="13" t="n">
         <v>140</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G417" s="15" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="13" t="n">
         <v>141</v>
       </c>
@@ -11968,19 +11992,19 @@
         <v>89</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G418" s="15" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="13" t="n">
         <v>142</v>
       </c>
@@ -11988,22 +12012,22 @@
         <v>72</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G419" s="15" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="13" t="n">
         <v>143</v>
       </c>
@@ -12014,10 +12038,10 @@
         <v>44</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>80</v>
@@ -12026,30 +12050,30 @@
         <v>127</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="13" t="n">
         <v>144</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F421" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G421" s="15" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="13" t="n">
         <v>145</v>
       </c>
@@ -12057,10 +12081,10 @@
         <v>71</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>237</v>
@@ -12069,38 +12093,38 @@
         <v>84</v>
       </c>
       <c r="G422" s="15" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="13" t="n">
         <v>146</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G423" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="13" t="n">
         <v>147</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>44</v>
@@ -12112,13 +12136,13 @@
         <v>86</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G424" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="13" t="n">
         <v>148</v>
       </c>
@@ -12126,30 +12150,30 @@
         <v>71</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G425" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="13" t="n">
         <v>149</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>86</v>
@@ -12158,82 +12182,82 @@
         <v>183</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G426" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="13" t="n">
         <v>150</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>80</v>
       </c>
       <c r="G427" s="15" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="13" t="n">
         <v>151</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="F428" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G428" s="15" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="13" t="n">
         <v>152</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>371</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G429" s="15" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="13" t="n">
         <v>153</v>
       </c>
@@ -12241,56 +12265,56 @@
         <v>68</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="G430" s="15" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="13" t="n">
         <v>154</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G431" s="15" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="13" t="n">
         <v>155</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>45</v>
@@ -12302,12 +12326,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="13" t="n">
         <v>156</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>46</v>
@@ -12325,15 +12349,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="13" t="n">
         <v>157</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>82</v>
@@ -12348,12 +12372,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="13" t="n">
         <v>158</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>93</v>
@@ -12365,13 +12389,13 @@
         <v>44</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G435" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="13" t="n">
         <v>159</v>
       </c>
@@ -12382,19 +12406,19 @@
         <v>213</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G436" s="15" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="13" t="n">
         <v>160</v>
       </c>
@@ -12405,27 +12429,27 @@
         <v>379</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G437" s="15" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="13" t="n">
         <v>161</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>47</v>
@@ -12434,18 +12458,18 @@
         <v>104</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="G438" s="15" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="13" t="n">
         <v>162</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>44</v>
@@ -12457,18 +12481,18 @@
         <v>127</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G439" s="15" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="13" t="n">
         <v>163</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>46</v>
@@ -12477,16 +12501,16 @@
         <v>86</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G440" s="15" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="13" t="n">
         <v>164</v>
       </c>
@@ -12494,10 +12518,10 @@
         <v>88</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>120</v>
@@ -12509,7 +12533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="13" t="n">
         <v>165</v>
       </c>
@@ -12520,19 +12544,19 @@
         <v>93</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G442" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="13" t="n">
         <v>166</v>
       </c>
@@ -12540,22 +12564,22 @@
         <v>90</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G443" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="13" t="n">
         <v>167</v>
       </c>
@@ -12566,19 +12590,19 @@
         <v>17</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G444" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="13" t="n">
         <v>168</v>
       </c>
@@ -12586,10 +12610,10 @@
         <v>93</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>44</v>
@@ -12598,18 +12622,18 @@
         <v>82</v>
       </c>
       <c r="G445" s="15" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="13" t="n">
         <v>169</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>86</v>
@@ -12618,10 +12642,10 @@
         <v>84</v>
       </c>
       <c r="G446" s="15" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="13" t="n">
         <v>170</v>
       </c>
@@ -12635,93 +12659,93 @@
         <v>71</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="G447" s="15" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="13" t="n">
         <v>171</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>136</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G448" s="15" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="13" t="n">
         <v>172</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G449" s="15" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="13" t="n">
         <v>173</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G450" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="13" t="n">
         <v>174</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F451" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G451" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="13" t="n">
         <v>175</v>
       </c>
@@ -12735,61 +12759,61 @@
         <v>152</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G452" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="13" t="n">
         <v>176</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>221</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="G453" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="13" t="n">
         <v>177</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G454" s="15" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="13" t="n">
         <v>178</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>127</v>
@@ -12798,10 +12822,10 @@
         <v>80</v>
       </c>
       <c r="G455" s="15" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="13" t="n">
         <v>179</v>
       </c>
@@ -12809,19 +12833,19 @@
         <v>88</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G456" s="15" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="13" t="n">
         <v>180</v>
       </c>
@@ -12829,7 +12853,7 @@
         <v>89</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>79</v>
@@ -12838,10 +12862,10 @@
         <v>84</v>
       </c>
       <c r="G457" s="15" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="13" t="n">
         <v>181</v>
       </c>
@@ -12849,19 +12873,19 @@
         <v>90</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G458" s="15" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="13" t="n">
         <v>182</v>
       </c>
@@ -12869,19 +12893,19 @@
         <v>91</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G459" s="15" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="13" t="n">
         <v>183</v>
       </c>
@@ -12889,39 +12913,39 @@
         <v>93</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F460" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G460" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="13" t="n">
         <v>184</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>132</v>
       </c>
       <c r="G461" s="15" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="13" t="n">
         <v>185</v>
       </c>
@@ -12935,18 +12959,18 @@
         <v>237</v>
       </c>
       <c r="F462" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="G462" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="13" t="n">
         <v>186</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D463" s="2" t="s">
         <v>86</v>
@@ -12955,21 +12979,21 @@
         <v>44</v>
       </c>
       <c r="F463" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="G463" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="13" t="n">
         <v>187</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>86</v>
@@ -12981,15 +13005,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="13" t="n">
         <v>188</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>181</v>
@@ -12998,18 +13022,18 @@
         <v>82</v>
       </c>
       <c r="G465" s="15" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="13" t="n">
         <v>189</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>183</v>
@@ -13021,7 +13045,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="13" t="n">
         <v>190</v>
       </c>
@@ -13035,58 +13059,58 @@
         <v>74</v>
       </c>
       <c r="F467" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G467" s="15" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="13" t="n">
         <v>191</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>189</v>
       </c>
       <c r="F468" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G468" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="13" t="n">
         <v>192</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F469" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="G469" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="13" t="n">
         <v>193</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D470" s="2" t="s">
         <v>47</v>
@@ -13095,13 +13119,13 @@
         <v>152</v>
       </c>
       <c r="F470" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="G470" s="15" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="13" t="n">
         <v>194</v>
       </c>
@@ -13115,13 +13139,13 @@
         <v>216</v>
       </c>
       <c r="F471" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="G471" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="13" t="n">
         <v>195</v>
       </c>
@@ -13135,13 +13159,13 @@
         <v>221</v>
       </c>
       <c r="F472" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="G472" s="15" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="13" t="n">
         <v>196</v>
       </c>
@@ -13149,19 +13173,19 @@
         <v>90</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F473" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="G473" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="13" t="n">
         <v>197</v>
       </c>
@@ -13169,19 +13193,19 @@
         <v>91</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F474" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G474" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="13" t="n">
         <v>198</v>
       </c>
@@ -13189,59 +13213,59 @@
         <v>93</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F475" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="G475" s="15" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="13" t="n">
         <v>199</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>235</v>
       </c>
       <c r="F476" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G476" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="13" t="n">
         <v>200</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F477" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G477" s="15" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="13" t="n">
         <v>201</v>
       </c>
@@ -13249,7 +13273,7 @@
         <v>88</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>104</v>
@@ -13261,7 +13285,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="13" t="n">
         <v>202</v>
       </c>
@@ -13269,7 +13293,7 @@
         <v>89</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>44</v>
@@ -13281,7 +13305,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="13" t="n">
         <v>203</v>
       </c>
@@ -13289,7 +13313,7 @@
         <v>90</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>86</v>
@@ -13298,10 +13322,10 @@
         <v>141</v>
       </c>
       <c r="G480" s="15" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="13" t="n">
         <v>204</v>
       </c>
@@ -13309,19 +13333,19 @@
         <v>91</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>181</v>
       </c>
       <c r="F481" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="G481" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="13" t="n">
         <v>205</v>
       </c>
@@ -13329,7 +13353,7 @@
         <v>93</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>183</v>
@@ -13338,50 +13362,50 @@
         <v>72</v>
       </c>
       <c r="G482" s="15" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="13" t="n">
         <v>206</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F483" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G483" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="13" t="n">
         <v>207</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>245</v>
       </c>
       <c r="F484" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="G484" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="13" t="n">
         <v>208</v>
       </c>
@@ -13389,44 +13413,44 @@
         <v>68</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F485" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G485" s="15" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="13" t="n">
         <v>209</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F486" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G486" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="13" t="n">
         <v>210</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D487" s="2" t="s">
         <v>47</v>
@@ -13435,18 +13459,18 @@
         <v>409</v>
       </c>
       <c r="F487" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="G487" s="15" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="13" t="n">
         <v>211</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>82</v>
@@ -13455,33 +13479,33 @@
         <v>103</v>
       </c>
       <c r="F488" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="G488" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="13" t="n">
         <v>212</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>185</v>
       </c>
       <c r="F489" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="G489" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="13" t="n">
         <v>213</v>
       </c>
@@ -13489,19 +13513,19 @@
         <v>68</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F490" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G490" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="13" t="n">
         <v>214</v>
       </c>
@@ -13515,33 +13539,33 @@
         <v>196</v>
       </c>
       <c r="F491" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G491" s="15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="13" t="n">
         <v>215</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>188</v>
       </c>
       <c r="F492" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G492" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="13" t="n">
         <v>216</v>
       </c>
@@ -13549,132 +13573,132 @@
         <v>214</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F493" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="G493" s="15" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="13" t="n">
         <v>217</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F494" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G494" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="13" t="n">
         <v>218</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F495" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G495" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="13" t="n">
         <v>219</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F496" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G496" s="15" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="13" t="n">
         <v>220</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F497" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G497" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="13" t="n">
         <v>221</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F498" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G498" s="15" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="13" t="n">
         <v>222</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F499" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G499" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="13" t="n">
         <v>223</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F500" s="2" t="s">
         <v>28</v>
@@ -13683,7 +13707,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="13" t="n">
         <v>224</v>
       </c>
@@ -13691,24 +13715,24 @@
         <v>68</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F501" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G501" s="15" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="13" t="n">
         <v>225</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="F502" s="2" t="s">
         <v>32</v>
@@ -13717,32 +13741,32 @@
         <v>48</v>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="13" t="n">
         <v>226</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F503" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G503" s="15" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="13" t="n">
         <v>227</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>13</v>
@@ -13751,38 +13775,38 @@
         <v>44</v>
       </c>
     </row>
-    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="13" t="n">
         <v>228</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G505" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="13" t="n">
         <v>229</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G506" s="15" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="13" t="n">
         <v>230</v>
       </c>
@@ -13790,13 +13814,13 @@
         <v>88</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G507" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="13" t="n">
         <v>231</v>
       </c>
@@ -13804,13 +13828,13 @@
         <v>89</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G508" s="15" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="13" t="n">
         <v>232</v>
       </c>
@@ -13824,7 +13848,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="13" t="n">
         <v>233</v>
       </c>
@@ -13838,7 +13862,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="13" t="n">
         <v>234</v>
       </c>
@@ -13849,15 +13873,15 @@
         <v>32</v>
       </c>
       <c r="G511" s="15" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="512" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="13" t="n">
         <v>235</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D512" s="2" t="s">
         <v>34</v>
@@ -13866,21 +13890,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="13" t="n">
         <v>236</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G513" s="15" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="514" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="13" t="n">
         <v>237</v>
       </c>
@@ -13888,24 +13912,24 @@
         <v>402</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G514" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="13" t="n">
         <v>238</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="G515" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="13" t="n">
         <v>239</v>
       </c>
@@ -13916,29 +13940,29 @@
         <v>48</v>
       </c>
     </row>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="13" t="n">
         <v>240</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="G517" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="13" t="n">
         <v>241</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G518" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="13" t="n">
         <v>242</v>
       </c>
@@ -13949,7 +13973,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="13" t="n">
         <v>243</v>
       </c>
@@ -13960,7 +13984,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="13" t="n">
         <v>244</v>
       </c>
@@ -13971,7 +13995,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="13" t="n">
         <v>245</v>
       </c>
@@ -13982,7 +14006,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="13" t="n">
         <v>246</v>
       </c>
@@ -13993,40 +14017,40 @@
         <v>44</v>
       </c>
     </row>
-    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="13" t="n">
         <v>247</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="G524" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="13" t="n">
         <v>248</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G525" s="15" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="13" t="n">
         <v>249</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="G526" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="13" t="n">
         <v>250</v>
       </c>
@@ -14037,18 +14061,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="13" t="n">
         <v>251</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G528" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="13" t="n">
         <v>252</v>
       </c>
@@ -14059,18 +14083,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="13" t="n">
         <v>253</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G530" s="15" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="13" t="n">
         <v>254</v>
       </c>
@@ -14081,29 +14105,29 @@
         <v>238</v>
       </c>
     </row>
-    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="13" t="n">
         <v>255</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G532" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="13" t="n">
         <v>256</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="G533" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="13" t="n">
         <v>257</v>
       </c>
@@ -14114,7 +14138,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="13" t="n">
         <v>258</v>
       </c>
@@ -14125,51 +14149,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="13" t="n">
         <v>259</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="G536" s="15" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="13" t="n">
         <v>260</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G537" s="15" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="13" t="n">
         <v>261</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="G538" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="13" t="n">
         <v>262</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G539" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="13" t="n">
         <v>263</v>
       </c>
@@ -14180,40 +14204,40 @@
         <v>44</v>
       </c>
     </row>
-    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="13" t="n">
         <v>264</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="G541" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="13" t="n">
         <v>265</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="G542" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="13" t="n">
         <v>266</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G543" s="15" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="13" t="n">
         <v>267</v>
       </c>
@@ -14224,7 +14248,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="13" t="n">
         <v>268</v>
       </c>
@@ -14235,7 +14259,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="13" t="n">
         <v>269</v>
       </c>
@@ -14246,7 +14270,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="13" t="n">
         <v>270</v>
       </c>
@@ -14257,7 +14281,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="13" t="n">
         <v>271</v>
       </c>
@@ -14268,18 +14292,18 @@
         <v>253</v>
       </c>
     </row>
-    <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="13" t="n">
         <v>272</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G549" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="13" t="n">
         <v>273</v>
       </c>
@@ -14290,209 +14314,209 @@
         <v>409</v>
       </c>
     </row>
-    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="551" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="13" t="n">
         <v>274</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G551" s="15" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="13" t="n">
         <v>275</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="G552" s="15" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="13" t="n">
         <v>276</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G553" s="15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="13" t="n">
         <v>277</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="G554" s="15" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="13" t="n">
         <v>278</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="G555" s="15" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="13" t="n">
         <v>279</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="G556" s="15" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="13" t="n">
         <v>280</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="G557" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="13" t="n">
         <v>281</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G558" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="13" t="n">
         <v>282</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G559" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="560" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="13" t="n">
         <v>283</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G560" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="13" t="n">
         <v>284</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G561" s="15" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="562" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="13" t="n">
         <v>285</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G562" s="15"/>
     </row>
-    <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="563" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="13" t="n">
         <v>286</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G563" s="15"/>
     </row>
-    <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="564" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="13" t="n">
         <v>287</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G564" s="15"/>
     </row>
-    <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="13" t="n">
         <v>288</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G565" s="15"/>
     </row>
-    <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="566" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="13" t="n">
         <v>289</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G566" s="15"/>
     </row>
-    <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="567" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="13" t="n">
         <v>290</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G567" s="15"/>
     </row>
-    <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="13" t="n">
         <v>291</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G568" s="15"/>
     </row>
-    <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="569" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="13" t="n">
         <v>292</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G569" s="15"/>
     </row>
-    <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="13" t="n">
         <v>293</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G570" s="15"/>
     </row>
-    <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="571" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="13" t="n">
         <v>294</v>
       </c>
@@ -14501,7 +14525,7 @@
       </c>
       <c r="G571" s="15"/>
     </row>
-    <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="572" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="13" t="n">
         <v>295</v>
       </c>
@@ -14510,7 +14534,7 @@
       </c>
       <c r="G572" s="15"/>
     </row>
-    <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="573" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="13" t="n">
         <v>296</v>
       </c>
@@ -14519,7 +14543,7 @@
       </c>
       <c r="G573" s="15"/>
     </row>
-    <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="13" t="n">
         <v>297</v>
       </c>
@@ -14528,7 +14552,7 @@
       </c>
       <c r="G574" s="15"/>
     </row>
-    <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="13" t="n">
         <v>298</v>
       </c>
@@ -14537,35 +14561,35 @@
       </c>
       <c r="G575" s="15"/>
     </row>
-    <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="576" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="13" t="n">
         <v>299</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G576" s="15"/>
     </row>
-    <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="577" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B577" s="58" t="n">
+      <c r="B577" s="57" t="n">
         <v>299</v>
       </c>
-      <c r="C577" s="59" t="n">
+      <c r="C577" s="58" t="n">
         <v>168</v>
       </c>
-      <c r="D577" s="59" t="n">
+      <c r="D577" s="58" t="n">
         <v>237</v>
       </c>
-      <c r="E577" s="59" t="n">
+      <c r="E577" s="58" t="n">
         <v>217</v>
       </c>
-      <c r="F577" s="59" t="n">
+      <c r="F577" s="58" t="n">
         <v>228</v>
       </c>
-      <c r="G577" s="60" t="n">
+      <c r="G577" s="59" t="n">
         <v>284</v>
       </c>
       <c r="H577" s="26"/>
@@ -14589,9 +14613,6 @@
     <mergeCell ref="A194:G194"/>
     <mergeCell ref="A276:G276"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="D83" r:id="rId1" display="printf@PLT"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
